--- a/data/trans_orig/P1801_2016_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1801_2016_2023-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>190221</t>
+          <t>191295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>231973</t>
+          <t>234566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184364</t>
+          <t>184522</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>220722</t>
+          <t>219271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385601</t>
+          <t>385083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>441605</t>
+          <t>441138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,84%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197119</t>
+          <t>194526</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238871</t>
+          <t>237797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126333</t>
+          <t>127784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162691</t>
+          <t>162533</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>334542</t>
+          <t>335009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>390546</t>
+          <t>391064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,39%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168690</t>
+          <t>167418</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208537</t>
+          <t>207728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196349</t>
+          <t>198636</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234932</t>
+          <t>233924</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>377510</t>
+          <t>375243</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>433471</t>
+          <t>432376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168690</t>
+          <t>169499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>208537</t>
+          <t>209809</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>137341</t>
+          <t>138349</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>175924</t>
+          <t>173637</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316029</t>
+          <t>317124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371990</t>
+          <t>374257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,93%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>255648</t>
+          <t>253717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>301161</t>
+          <t>301132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93557</t>
+          <t>92993</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117647</t>
+          <t>118278</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>358037</t>
+          <t>356018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>411688</t>
+          <t>410010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>220753</t>
+          <t>220782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>266266</t>
+          <t>268197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48476</t>
+          <t>47845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72566</t>
+          <t>73130</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>276348</t>
+          <t>278026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329999</t>
+          <t>332018</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,26%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>520321</t>
+          <t>516548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>588632</t>
+          <t>585042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>422473</t>
+          <t>420367</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>482756</t>
+          <t>479278</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>957865</t>
+          <t>955660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1047396</t>
+          <t>1049724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>561006</t>
+          <t>564596</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>629317</t>
+          <t>633090</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>343120</t>
+          <t>346598</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>403403</t>
+          <t>405509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>928118</t>
+          <t>925790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1017649</t>
+          <t>1019854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,62%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>254056</t>
+          <t>257737</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>306173</t>
+          <t>306176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>381451</t>
+          <t>380679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>435689</t>
+          <t>434931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>652647</t>
+          <t>654261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>729403</t>
+          <t>726766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,48%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>314533</t>
+          <t>314530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>366650</t>
+          <t>362969</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>302555</t>
+          <t>303313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>356793</t>
+          <t>357565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>629547</t>
+          <t>632184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>706303</t>
+          <t>704689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52966</t>
+          <t>54469</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82419</t>
+          <t>82437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>603612</t>
+          <t>604676</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>667831</t>
+          <t>667504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>664837</t>
+          <t>667632</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>741302</t>
+          <t>742526</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,23%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204726</t>
+          <t>204708</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234179</t>
+          <t>232676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>414194</t>
+          <t>414521</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>478413</t>
+          <t>477349</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>627868</t>
+          <t>626644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>704333</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1520488</t>
+          <t>1520197</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1639118</t>
+          <t>1635309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1956487</t>
+          <t>1959298</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2078073</t>
+          <t>2077113</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3512040</t>
+          <t>3507528</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3677444</t>
+          <t>3675336</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1746604</t>
+          <t>1750413</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1865234</t>
+          <t>1865525</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1453523</t>
+          <t>1454483</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1575109</t>
+          <t>1572298</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3239874</t>
+          <t>3241982</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3405278</t>
+          <t>3409790</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -3361,22 +3361,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>271138</t>
+          <t>295659</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>248403</t>
+          <t>270737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>294224</t>
+          <t>320824</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3396,32 +3396,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>275280</t>
+          <t>305232</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>257046</t>
+          <t>285820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>293210</t>
+          <t>323886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3431,32 +3431,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>546418</t>
+          <t>600891</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>515027</t>
+          <t>568281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>573293</t>
+          <t>631834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -3474,27 +3474,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>233030</t>
+          <t>253832</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>209944</t>
+          <t>228667</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255765</t>
+          <t>278754</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3509,32 +3509,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>170480</t>
+          <t>181406</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152550</t>
+          <t>162752</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>188714</t>
+          <t>200818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3544,32 +3544,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>403510</t>
+          <t>435238</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>376635</t>
+          <t>404295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>434901</t>
+          <t>467848</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -3587,17 +3587,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504168</t>
+          <t>549491</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504168</t>
+          <t>549491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504168</t>
+          <t>549491</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3622,17 +3622,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445760</t>
+          <t>486638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>445760</t>
+          <t>486638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445760</t>
+          <t>486638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>949928</t>
+          <t>1036129</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>949928</t>
+          <t>1036129</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>949928</t>
+          <t>1036129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3704,32 +3704,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>259200</t>
+          <t>268131</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>236066</t>
+          <t>245512</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>279839</t>
+          <t>290374</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3739,32 +3739,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>215511</t>
+          <t>236791</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>198339</t>
+          <t>218618</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>232643</t>
+          <t>254788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>474711</t>
+          <t>504922</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>446293</t>
+          <t>477559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>502290</t>
+          <t>533568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3817,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>193013</t>
+          <t>215081</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172374</t>
+          <t>192838</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216147</t>
+          <t>237700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3852,32 +3852,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>166389</t>
+          <t>185689</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149257</t>
+          <t>167692</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183561</t>
+          <t>203862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3887,32 +3887,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>359401</t>
+          <t>400770</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>331822</t>
+          <t>372124</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>387819</t>
+          <t>428133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,27%</t>
         </is>
       </c>
     </row>
@@ -3930,17 +3930,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381900</t>
+          <t>422480</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381900</t>
+          <t>422480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381900</t>
+          <t>422480</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834112</t>
+          <t>905692</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834112</t>
+          <t>905692</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834112</t>
+          <t>905692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4047,32 +4047,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>470049</t>
+          <t>244490</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>343856</t>
+          <t>223025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>591707</t>
+          <t>268004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4082,32 +4082,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>95697</t>
+          <t>107964</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84937</t>
+          <t>96037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106294</t>
+          <t>119158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4117,32 +4117,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>565746</t>
+          <t>352454</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>447116</t>
+          <t>326593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>721396</t>
+          <t>376446</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -4160,32 +4160,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>198215</t>
+          <t>227122</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76557</t>
+          <t>203608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>324408</t>
+          <t>248587</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4195,32 +4195,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70595</t>
+          <t>78858</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59998</t>
+          <t>67664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>81355</t>
+          <t>90785</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4230,32 +4230,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>268810</t>
+          <t>305980</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113160</t>
+          <t>281988</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>387440</t>
+          <t>331841</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -4273,17 +4273,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4308,17 +4308,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834556</t>
+          <t>658434</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834556</t>
+          <t>658434</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834556</t>
+          <t>658434</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4390,32 +4390,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518011</t>
+          <t>553653</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>483696</t>
+          <t>520488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>553483</t>
+          <t>593289</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4425,32 +4425,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>655395</t>
+          <t>504051</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>557584</t>
+          <t>477532</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>814499</t>
+          <t>529436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4460,32 +4460,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1173406</t>
+          <t>1057704</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1058730</t>
+          <t>1011192</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1418379</t>
+          <t>1102647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -4503,32 +4503,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>515818</t>
+          <t>577119</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>480346</t>
+          <t>537483</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>550133</t>
+          <t>610284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4538,32 +4538,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>321970</t>
+          <t>354899</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162866</t>
+          <t>329514</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>419781</t>
+          <t>381418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4573,32 +4573,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>837788</t>
+          <t>932019</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>592815</t>
+          <t>887076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>952464</t>
+          <t>978531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033829</t>
+          <t>1130772</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033829</t>
+          <t>1130772</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033829</t>
+          <t>1130772</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977365</t>
+          <t>858950</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977365</t>
+          <t>858950</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977365</t>
+          <t>858950</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4686,17 +4686,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2011194</t>
+          <t>1989723</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2011194</t>
+          <t>1989723</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2011194</t>
+          <t>1989723</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4733,32 +4733,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>225149</t>
+          <t>247687</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>202443</t>
+          <t>222781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>249835</t>
+          <t>275628</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>431771</t>
+          <t>474652</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>326494</t>
+          <t>451025</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>490124</t>
+          <t>498797</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4803,32 +4803,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>656920</t>
+          <t>722340</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>551577</t>
+          <t>685763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>712163</t>
+          <t>755818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -4846,32 +4846,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>248615</t>
+          <t>319198</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>223929</t>
+          <t>291257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>271321</t>
+          <t>344104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4881,32 +4881,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>408643</t>
+          <t>355309</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>350290</t>
+          <t>331164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>513920</t>
+          <t>378936</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4916,32 +4916,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>657258</t>
+          <t>674506</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>602015</t>
+          <t>641028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>762601</t>
+          <t>711083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -4959,17 +4959,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473764</t>
+          <t>566885</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473764</t>
+          <t>566885</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473764</t>
+          <t>566885</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4994,17 +4994,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840414</t>
+          <t>829961</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840414</t>
+          <t>829961</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840414</t>
+          <t>829961</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5029,17 +5029,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1314178</t>
+          <t>1396846</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1314178</t>
+          <t>1396846</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1314178</t>
+          <t>1396846</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5076,32 +5076,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>46537</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33517</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>77389</t>
+          <t>66383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5111,32 +5111,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>366302</t>
+          <t>399375</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>342103</t>
+          <t>371631</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>394514</t>
+          <t>428604</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5146,32 +5146,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>418379</t>
+          <t>445912</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>385932</t>
+          <t>411019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>453494</t>
+          <t>481046</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>44,53%</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5189,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>188429</t>
+          <t>190691</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163118</t>
+          <t>170845</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206990</t>
+          <t>206883</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5224,32 +5224,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>393874</t>
+          <t>443683</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>365662</t>
+          <t>414454</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>418073</t>
+          <t>471427</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5259,32 +5259,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>582304</t>
+          <t>634374</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>547189</t>
+          <t>599240</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>614751</t>
+          <t>669267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,95%</t>
         </is>
       </c>
     </row>
@@ -5302,17 +5302,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760176</t>
+          <t>843058</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760176</t>
+          <t>843058</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760176</t>
+          <t>843058</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5372,17 +5372,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000683</t>
+          <t>1080286</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000683</t>
+          <t>1080286</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000683</t>
+          <t>1080286</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1795625</t>
+          <t>1656157</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1642342</t>
+          <t>1596604</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2163322</t>
+          <t>1726965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5454,32 +5454,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2039955</t>
+          <t>2028065</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1907111</t>
+          <t>1976256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2312098</t>
+          <t>2082494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5489,32 +5489,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3835580</t>
+          <t>3684222</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3621290</t>
+          <t>3603539</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4245117</t>
+          <t>3775643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>53,43%</t>
         </is>
       </c>
     </row>
@@ -5532,32 +5532,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1577120</t>
+          <t>1783043</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1209423</t>
+          <t>1712235</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1730403</t>
+          <t>1842596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5567,32 +5567,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1531951</t>
+          <t>1599845</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1259808</t>
+          <t>1545416</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1664795</t>
+          <t>1651654</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5602,32 +5602,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3109071</t>
+          <t>3382888</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2699534</t>
+          <t>3291467</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3323361</t>
+          <t>3463571</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -5645,17 +5645,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3372745</t>
+          <t>3439200</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3372745</t>
+          <t>3439200</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3372745</t>
+          <t>3439200</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5680,17 +5680,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3571906</t>
+          <t>3627910</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3571906</t>
+          <t>3627910</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3571906</t>
+          <t>3627910</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5715,17 +5715,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6944651</t>
+          <t>7067110</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6944651</t>
+          <t>7067110</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6944651</t>
+          <t>7067110</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
